--- a/resumen_rendiciones.xlsx
+++ b/resumen_rendiciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:Y37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,12 +446,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>M1 1 Moraleja 2025</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>M1 1 Moraleja 2025</t>
+          <t>M1 10 Moraleja 2025</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -461,30 +461,95 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>M1 3 Moraleja 2025</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>M1 4 Moraleja 2025</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>M1 5 Moraleja 2025</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>M1 6 Moraleja 2025</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>M1 7 Moraleja 2025</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>M1 8 Moraleja 2025</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>M1 9 Moraleja 2025</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>M1 Invierno Ad.26</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>M2 1 Moraleja 2025</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>M2 10 Moraleja 2025</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>M2 2 Moraleja 2025</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>M2 3 Moraleja 2025</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>M2 4 Moraleja 2025</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>M2 5 Moraleja 2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>M2 6 Moraleja 2025</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>M2 7 Moraleja 2025</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>M2 8 Moraleja 2025</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>M2 9 Moraleja 2025</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>M2 Invierno Ad.26</t>
         </is>
@@ -506,13 +571,13 @@
           <t>Acuña</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
+      <c r="D2" t="n">
         <v>29</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
       </c>
       <c r="F2" t="n">
         <v>26</v>
@@ -522,23 +587,88 @@
           <t>NR</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
         <v>57</v>
       </c>
-      <c r="I2" t="n">
+      <c r="O2" t="n">
         <v>8</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
@@ -560,14 +690,14 @@
           <t>Arriagada</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
+      <c r="D3" t="n">
         <v>42</v>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>NR</t>
@@ -578,23 +708,88 @@
           <t>NR</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
         <v>51</v>
       </c>
-      <c r="I3" t="n">
+      <c r="O3" t="n">
         <v>15</v>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
@@ -659,6 +854,71 @@
           <t>NR</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -676,39 +936,104 @@
           <t>Bravo</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
+      <c r="D5" t="n">
         <v>31</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
       </c>
       <c r="F5" t="n">
         <v>27</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
         <v>26</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
         <v>47</v>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
@@ -730,14 +1055,14 @@
           <t>Carrera</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
+      <c r="D6" t="n">
         <v>34</v>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>NR</t>
@@ -748,25 +1073,90 @@
           <t>NR</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
         <v>50</v>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
@@ -788,13 +1178,13 @@
           <t>Catalán</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
+      <c r="D7" t="n">
         <v>13</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
       </c>
       <c r="F7" t="n">
         <v>12</v>
@@ -804,25 +1194,90 @@
           <t>NR</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
         <v>34</v>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
@@ -844,14 +1299,14 @@
           <t>Cruz</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
+      <c r="D8" t="n">
         <v>40</v>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>NR</t>
@@ -862,25 +1317,90 @@
           <t>NR</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
         <v>57</v>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
@@ -922,25 +1442,90 @@
           <t>NR</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
         <v>57</v>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
@@ -962,13 +1547,13 @@
           <t>Fontecilla</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
+      <c r="D10" t="n">
         <v>34</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
       </c>
       <c r="F10" t="n">
         <v>37</v>
@@ -978,25 +1563,90 @@
           <t>NR</t>
         </is>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
         <v>49</v>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
@@ -1018,13 +1668,13 @@
           <t>Galleguillos</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
+      <c r="D11" t="n">
         <v>18</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
       </c>
       <c r="F11" t="n">
         <v>15</v>
@@ -1039,16 +1689,81 @@
           <t>NR</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
         <v>15</v>
       </c>
-      <c r="J11" t="n">
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
         <v>15</v>
       </c>
-      <c r="K11" t="n">
+      <c r="T11" t="n">
         <v>20</v>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
@@ -1070,14 +1785,14 @@
           <t>García</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
+      <c r="D12" t="n">
         <v>30</v>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>NR</t>
@@ -1088,25 +1803,90 @@
           <t>NR</t>
         </is>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
         <v>50</v>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
@@ -1148,25 +1928,90 @@
           <t>NR</t>
         </is>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
         <v>48</v>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
@@ -1188,14 +2033,14 @@
           <t>Gutierrez</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
+      <c r="D14" t="n">
         <v>28</v>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>NR</t>
@@ -1206,25 +2051,90 @@
           <t>NR</t>
         </is>
       </c>
-      <c r="H14" t="n">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
         <v>49</v>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
@@ -1246,14 +2156,14 @@
           <t>Huechucura</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
+      <c r="D15" t="n">
         <v>16</v>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>NR</t>
@@ -1285,6 +2195,71 @@
         </is>
       </c>
       <c r="L15" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
@@ -1306,14 +2281,14 @@
           <t>Larenas</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
+      <c r="D16" t="n">
         <v>21</v>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>NR</t>
@@ -1345,6 +2320,71 @@
         </is>
       </c>
       <c r="L16" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
@@ -1366,14 +2406,14 @@
           <t>Lazo</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
+      <c r="D17" t="n">
         <v>34</v>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>NR</t>
@@ -1405,6 +2445,71 @@
         </is>
       </c>
       <c r="L17" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
@@ -1426,13 +2531,13 @@
           <t>Lizana</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
+      <c r="D18" t="n">
         <v>45</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
       </c>
       <c r="F18" t="n">
         <v>39</v>
@@ -1447,16 +2552,79 @@
           <t>NR</t>
         </is>
       </c>
-      <c r="I18" t="n">
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
         <v>20</v>
       </c>
-      <c r="J18" t="n">
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>34</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="S18" t="n">
         <v>37</v>
       </c>
-      <c r="K18" t="n">
+      <c r="T18" t="n">
         <v>37</v>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
@@ -1478,41 +2646,104 @@
           <t>Lorca</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
+      <c r="D19" t="n">
         <v>30</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
       </c>
       <c r="F19" t="n">
         <v>17</v>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
+      <c r="G19" t="n">
+        <v>22</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
         <v>49</v>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
@@ -1557,20 +2788,85 @@
           <t>NR</t>
         </is>
       </c>
-      <c r="I20" t="n">
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
         <v>30</v>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
@@ -1610,25 +2906,90 @@
           <t>NR</t>
         </is>
       </c>
-      <c r="H21" t="n">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
         <v>44</v>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
@@ -1650,14 +3011,14 @@
           <t>Olguín</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
+      <c r="D22" t="n">
         <v>34</v>
       </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>NR</t>
@@ -1668,25 +3029,90 @@
           <t>NR</t>
         </is>
       </c>
-      <c r="H22" t="n">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
         <v>47</v>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
@@ -1726,25 +3152,90 @@
           <t>NR</t>
         </is>
       </c>
-      <c r="H23" t="n">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
         <v>53</v>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
@@ -1766,13 +3257,13 @@
           <t>Ortiz</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
+      <c r="D24" t="n">
         <v>43</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
       </c>
       <c r="F24" t="n">
         <v>43</v>
@@ -1782,25 +3273,90 @@
           <t>NR</t>
         </is>
       </c>
-      <c r="H24" t="n">
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
         <v>52</v>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y24" t="n">
         <v>26</v>
       </c>
     </row>
@@ -1820,14 +3376,14 @@
           <t>Parraguez</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
+      <c r="D25" t="n">
         <v>36</v>
       </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>NR</t>
@@ -1862,6 +3418,69 @@
         <is>
           <t>NR</t>
         </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y25" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="26">
@@ -1880,13 +3499,13 @@
           <t>Quilodrán</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
+      <c r="D26" t="n">
         <v>57</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
       </c>
       <c r="F26" t="n">
         <v>56</v>
@@ -1917,6 +3536,71 @@
         </is>
       </c>
       <c r="L26" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
@@ -1938,13 +3622,13 @@
           <t>Quilodrán</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
+      <c r="D27" t="n">
         <v>56</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
       </c>
       <c r="F27" t="n">
         <v>55</v>
@@ -1975,6 +3659,71 @@
         </is>
       </c>
       <c r="L27" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
@@ -2009,14 +3758,14 @@
       <c r="F28" t="n">
         <v>41</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
         <v>37</v>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>NR</t>
@@ -2033,6 +3782,71 @@
         </is>
       </c>
       <c r="L28" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
@@ -2054,14 +3868,14 @@
           <t>Reyes</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
+      <c r="D29" t="n">
         <v>48</v>
       </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
           <t>NR</t>
@@ -2093,6 +3907,71 @@
         </is>
       </c>
       <c r="L29" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
@@ -2114,14 +3993,14 @@
           <t>Robles</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
+      <c r="D30" t="n">
         <v>27</v>
       </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>NR</t>
@@ -2132,25 +4011,90 @@
           <t>NR</t>
         </is>
       </c>
-      <c r="H30" t="n">
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
         <v>43</v>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
@@ -2172,37 +4116,100 @@
           <t>Rojas</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
+      <c r="D31" t="n">
         <v>41</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
       </c>
       <c r="F31" t="n">
         <v>49</v>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
+      <c r="G31" t="n">
+        <v>41</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="I31" t="n">
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
         <v>20</v>
       </c>
-      <c r="J31" t="n">
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="S31" t="n">
         <v>39</v>
       </c>
-      <c r="K31" t="n">
+      <c r="T31" t="n">
         <v>33</v>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
@@ -2224,13 +4231,13 @@
           <t>Sotelo</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
+      <c r="D32" t="n">
         <v>34</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
       </c>
       <c r="F32" t="n">
         <v>30</v>
@@ -2240,25 +4247,90 @@
           <t>NR</t>
         </is>
       </c>
-      <c r="H32" t="n">
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
         <v>53</v>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
@@ -2280,13 +4352,13 @@
           <t>Tobar</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
+      <c r="D33" t="n">
         <v>36</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
       </c>
       <c r="F33" t="n">
         <v>38</v>
@@ -2301,18 +4373,83 @@
           <t>NR</t>
         </is>
       </c>
-      <c r="I33" t="n">
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
         <v>15</v>
       </c>
-      <c r="J33" t="n">
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="S33" t="n">
         <v>28</v>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
@@ -2334,14 +4471,14 @@
           <t>Urrucelqui</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
+      <c r="D34" t="n">
         <v>32</v>
       </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>NR</t>
@@ -2352,25 +4489,90 @@
           <t>NR</t>
         </is>
       </c>
-      <c r="H34" t="n">
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
         <v>55</v>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
@@ -2392,41 +4594,106 @@
           <t>Valenzuela</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
+      <c r="D35" t="n">
         <v>29</v>
       </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="G35" t="n">
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
         <v>34</v>
       </c>
-      <c r="H35" t="n">
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
         <v>54</v>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L35" t="n">
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y35" t="n">
         <v>39</v>
       </c>
     </row>
@@ -2446,13 +4713,13 @@
           <t>Vargas</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
+      <c r="D36" t="n">
         <v>26</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
       </c>
       <c r="F36" t="n">
         <v>17</v>
@@ -2462,25 +4729,90 @@
           <t>NR</t>
         </is>
       </c>
-      <c r="H36" t="n">
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
         <v>37</v>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
@@ -2541,6 +4873,71 @@
         </is>
       </c>
       <c r="L37" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
